--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135531037</v>
+        <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,20 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>djupsjön, Nrk</t>
+          <t>djupsjön, djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506897</v>
+        <v>506896</v>
       </c>
       <c r="R2" t="n">
-        <v>6531612</v>
+        <v>6531547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska Hel Tall</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +796,7 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135531037</t>
+          <t>https://artportalen.se/Sighting/135930097</t>
         </is>
       </c>
     </row>
@@ -921,6 +922,128 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135531493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135930067</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>djupsjön, djupsjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506897</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6531582</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135930067</t>
         </is>
       </c>
     </row>
@@ -928,6 +1051,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135531493</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18232-2026 artfynd.xlsx
+++ b/artfynd/A 18232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135930097</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135930067</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
